--- a/data/trans_dic/P56$amigo-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P56$amigo-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda sus amistades cuando tiene dificultades en la actividades básicas</t>
+          <t>Población a la que, al menos, le ayuda sus amistades cuando tiene dificultades en la actividades básicas (tasa de respuesta: 96,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 8,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,78</t>
+          <t>0,0; 11,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,35</t>
+          <t>0,0; 12,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,63</t>
+          <t>0,0; 14,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,3</t>
+          <t>0,0; 3,34</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 6,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,73</t>
+          <t>0,0; 10,31</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,05</t>
+          <t>0,0; 9,15</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,64</t>
+          <t>0,0; 3,59</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,67; 47,45</t>
+          <t>0,0; 46,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 6,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 8,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,3</t>
+          <t>0,0; 9,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 7,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 3,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,29</t>
+          <t>0,0; 12,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,44; 8,23</t>
+          <t>1,44; 8,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,31; 19,17</t>
+          <t>2,34; 19,7</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,39</t>
+          <t>0,0; 10,04</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 6,66</t>
+          <t>1,17; 6,8</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,95</t>
+          <t>0,0; 25,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,32; 20,02</t>
+          <t>2,23; 18,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 6,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,45; 13,16</t>
+          <t>1,42; 12,87</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 7,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,75; 16,74</t>
+          <t>1,74; 14,75</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 4,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,81; 13,41</t>
+          <t>2,43; 13,55</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,38</t>
+          <t>0,0; 15,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,23</t>
+          <t>0,0; 19,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,58</t>
+          <t>0,0; 10,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,2</t>
+          <t>0,0; 11,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,2; 9,86</t>
+          <t>2,17; 9,99</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,27</t>
+          <t>0,0; 14,12</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,52</t>
+          <t>0,0; 7,97</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,22</t>
+          <t>0,0; 9,41</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,6; 8,63</t>
+          <t>2,21; 9,0</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,09; 16,78</t>
+          <t>2,1; 15,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,45; 8,24</t>
+          <t>1,61; 8,32</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,53</t>
+          <t>0,0; 7,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,05; 5,93</t>
+          <t>1,01; 5,9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 5,57</t>
+          <t>0,57; 4,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,29; 6,0</t>
+          <t>2,31; 5,83</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,36; 7,32</t>
+          <t>1,39; 8,16</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,75; 4,21</t>
+          <t>0,73; 4,22</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,84</t>
+          <t>0,4; 3,79</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,48; 5,65</t>
+          <t>2,69; 5,81</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda sus amistades cuando tiene dificultades en la actividades básicas</t>
+          <t>Población a la que, al menos, le ayuda sus amistades cuando tiene dificultades en la actividades básicas (tasa de respuesta: 96,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1650</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 1808</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 1569</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 2203</t>
+          <t>0; 2924</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 1939</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4774</t>
+          <t>0; 5759</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 5426</t>
+          <t>0; 5618</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2041</t>
+          <t>0; 2068</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 1873</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 5520</t>
+          <t>0; 5848</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 4734</t>
+          <t>0; 5381</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 3165</t>
+          <t>0; 3117</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>998; 7102</t>
+          <t>0; 6996</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2059</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 1612</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2027</t>
+          <t>0; 2350</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 2084</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 2094</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 6689</t>
+          <t>0; 5049</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>963; 5504</t>
+          <t>961; 5547</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>980; 8118</t>
+          <t>990; 8341</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 2111</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 6293</t>
+          <t>0; 6081</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1146; 6085</t>
+          <t>1068; 6214</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1443</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2192</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 1852</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 5674</t>
+          <t>0; 5109</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 1859</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>980; 8446</t>
+          <t>939; 7773</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2304</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>614; 5557</t>
+          <t>601; 5435</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 1802</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>986; 9401</t>
+          <t>980; 8283</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 2187</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1760; 8382</t>
+          <t>1521; 8472</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1479</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2152</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 1690</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4960</t>
+          <t>0; 4929</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 7465</t>
+          <t>0; 6200</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 4398</t>
+          <t>0; 5352</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 7934</t>
+          <t>0; 6476</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1762; 7891</t>
+          <t>1734; 7999</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 6934</t>
+          <t>0; 6413</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 5477</t>
+          <t>0; 5802</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 5194</t>
+          <t>0; 6768</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2923; 9687</t>
+          <t>2486; 10110</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1008; 8102</t>
+          <t>1013; 7266</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 2178</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 1748</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1478; 8413</t>
+          <t>1640; 8489</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 7043</t>
+          <t>0; 6632</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2156; 12176</t>
+          <t>2069; 12115</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>974; 9572</t>
+          <t>973; 8504</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5751; 15073</t>
+          <t>5800; 14629</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1926; 10378</t>
+          <t>1978; 11567</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2136; 11953</t>
+          <t>2062; 11962</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>996; 9353</t>
+          <t>978; 9233</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>8772; 19937</t>
+          <t>9491; 20514</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P56$amigo-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P56$amigo-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,65</t>
+          <t>0,0; 9,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -742,17 +742,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,49</t>
+          <t>0,0; 12,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,11</t>
+          <t>0,0; 12,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,34</t>
+          <t>0,0; 3,5</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -762,17 +762,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,31</t>
+          <t>0,0; 10,05</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,15</t>
+          <t>0,0; 8,48</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,59</t>
+          <t>0,0; 3,38</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,74</t>
+          <t>6,74; 48,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,62</t>
+          <t>0,0; 6,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -887,17 +887,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,3</t>
+          <t>0,0; 14,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,44; 8,29</t>
+          <t>1,36; 8,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,34; 19,7</t>
+          <t>2,35; 20,04</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -907,12 +907,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,04</t>
+          <t>0,0; 11,35</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,17; 6,8</t>
+          <t>1,3; 6,47</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,17</t>
+          <t>0,0; 25,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,23; 18,42</t>
+          <t>2,4; 20,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,42; 12,87</t>
+          <t>1,42; 12,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,74; 14,75</t>
+          <t>1,76; 14,6</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,43; 13,55</t>
+          <t>2,55; 14,56</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -1152,47 +1152,47 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,29</t>
+          <t>0,0; 12,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,29</t>
+          <t>0,0; 22,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,44</t>
+          <t>0,0; 10,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,59</t>
+          <t>0,0; 9,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,17; 9,99</t>
+          <t>2,13; 9,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,12</t>
+          <t>0,0; 16,05</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,97</t>
+          <t>0,0; 7,65</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,41</t>
+          <t>0,0; 7,65</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,21; 9,0</t>
+          <t>2,53; 9,0</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,1; 15,05</t>
+          <t>2,1; 15,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1292,47 +1292,47 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,61; 8,32</t>
+          <t>1,39; 8,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,09</t>
+          <t>0,0; 7,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,01; 5,9</t>
+          <t>0,96; 5,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 4,95</t>
+          <t>0,56; 4,91</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,31; 5,83</t>
+          <t>2,37; 6,12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,39; 8,16</t>
+          <t>1,37; 7,98</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,73; 4,22</t>
+          <t>0,74; 4,18</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,79</t>
+          <t>0,4; 3,74</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,69; 5,81</t>
+          <t>2,45; 5,58</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>483</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>403</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>872</t>
+          <t>886</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 2924</t>
+          <t>0; 2535</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1670,17 +1670,17 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 5759</t>
+          <t>0; 5543</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 5618</t>
+          <t>0; 4904</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2068</t>
+          <t>0; 2301</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1690,17 +1690,17 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 5848</t>
+          <t>0; 5696</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 5381</t>
+          <t>0; 4985</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 3117</t>
+          <t>0; 3107</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>406</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2616</t>
+          <t>2824</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3001</t>
+          <t>3230</t>
         </is>
       </c>
     </row>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 6996</t>
+          <t>1009; 7217</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2350</t>
+          <t>0; 1806</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1883,17 +1883,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 5049</t>
+          <t>0; 5994</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>961; 5547</t>
+          <t>1006; 6138</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>990; 8341</t>
+          <t>997; 8483</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 6081</t>
+          <t>0; 6875</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1068; 6214</t>
+          <t>1301; 6484</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1738</t>
+          <t>1852</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2632</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4146</t>
+          <t>4484</t>
         </is>
       </c>
     </row>
@@ -2076,7 +2076,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 5109</t>
+          <t>0; 5988</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>939; 7773</t>
+          <t>1013; 8730</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>601; 5435</t>
+          <t>678; 6121</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>980; 8283</t>
+          <t>990; 8199</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1521; 8472</t>
+          <t>1804; 10308</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1422</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>4084</t>
+          <t>4381</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5506</t>
+          <t>5685</t>
         </is>
       </c>
     </row>
@@ -2284,47 +2284,47 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4929</t>
+          <t>0; 4178</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 6200</t>
+          <t>0; 7305</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 5352</t>
+          <t>0; 5324</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 6476</t>
+          <t>0; 5025</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1734; 7999</t>
+          <t>1871; 8600</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 6413</t>
+          <t>0; 7286</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 5802</t>
+          <t>0; 5572</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 6768</t>
+          <t>0; 5504</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2486; 10110</t>
+          <t>3064; 10896</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4016</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9509</t>
+          <t>10239</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13524</t>
+          <t>14284</t>
         </is>
       </c>
     </row>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1013; 7266</t>
+          <t>1012; 7720</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2492,47 +2492,47 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1640; 8489</t>
+          <t>1506; 8681</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 6632</t>
+          <t>0; 6763</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2069; 12115</t>
+          <t>1976; 11896</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>973; 8504</t>
+          <t>965; 8435</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5800; 14629</t>
+          <t>6525; 16865</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1978; 11567</t>
+          <t>1937; 11320</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2062; 11962</t>
+          <t>2090; 11859</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>978; 9233</t>
+          <t>977; 9130</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>9491; 20514</t>
+          <t>9414; 21425</t>
         </is>
       </c>
     </row>
